--- a/Sender Gmail Emails/CursoPLFrankPt2/Datos/Lista de Invitados.xlsx
+++ b/Sender Gmail Emails/CursoPLFrankPt2/Datos/Lista de Invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/CursoPLFrankPt2/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC0C2BD-5B1D-48DB-9B9F-71793491EEBD}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0780E6E-443B-4B58-A844-6AAB036C495D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
   </bookViews>
@@ -3030,6 +3030,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3351,6 +3355,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
     <col min="4" max="4" width="40.5703125" customWidth="1"/>
   </cols>

--- a/Sender Gmail Emails/CursoPLFrankPt2/Datos/Lista de Invitados.xlsx
+++ b/Sender Gmail Emails/CursoPLFrankPt2/Datos/Lista de Invitados.xlsx
@@ -3030,10 +3030,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/Sender Gmail Emails/CursoPLFrankPt2/Datos/Lista de Invitados.xlsx
+++ b/Sender Gmail Emails/CursoPLFrankPt2/Datos/Lista de Invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/CursoPLFrankPt2/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0780E6E-443B-4B58-A844-6AAB036C495D}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F11B224-9ACE-4D3B-8DA8-B3085A107215}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
   </bookViews>
@@ -2492,7 +2492,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2623,6 +2623,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2925,7 +2933,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -2968,12 +2976,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -3007,6 +3017,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -3028,6 +3039,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8413,7 +8428,7 @@
       <c r="C264" t="s">
         <v>814</v>
       </c>
-      <c r="D264" t="s">
+      <c r="D264" s="2" t="s">
         <v>815</v>
       </c>
       <c r="E264" t="s">
@@ -8472,6 +8487,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D264" r:id="rId1" xr:uid="{43A79DF7-27C1-4F27-9D47-74D1FF01C7AD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>